--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423898014371441</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>19021551</v>
+        <v>4510945</v>
       </c>
       <c r="L2" t="n">
-        <v>11549304</v>
+        <v>2540283</v>
       </c>
       <c r="M2" t="n">
-        <v>2985658</v>
+        <v>596155</v>
       </c>
       <c r="N2" t="n">
-        <v>178480</v>
+        <v>25186</v>
       </c>
       <c r="O2" t="n">
-        <v>1759886</v>
+        <v>372764</v>
       </c>
       <c r="P2" t="n">
-        <v>692613</v>
+        <v>152860</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999911785125732</v>
       </c>
       <c r="R2" t="n">
-        <v>0.938008189201355</v>
+        <v>0.8799850344657898</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8640785813331604</v>
+        <v>0.7590416073799133</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8338441252708435</v>
+        <v>0.7016989588737488</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6609660387039185</v>
+        <v>0.3540492355823517</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8701245188713074</v>
+        <v>0.7576581239700317</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9107996225357056</v>
+        <v>0.8308286070823669</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201873763595948</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>19021551</v>
+        <v>4510945</v>
       </c>
       <c r="E3" t="n">
-        <v>1227794</v>
+        <v>540188</v>
       </c>
       <c r="F3" t="n">
-        <v>13873</v>
+        <v>5967</v>
       </c>
       <c r="G3" t="n">
-        <v>2159</v>
+        <v>785</v>
       </c>
       <c r="H3" t="n">
-        <v>635</v>
+        <v>345</v>
       </c>
       <c r="I3" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="J3" t="n">
-        <v>40278333</v>
+        <v>10069564</v>
       </c>
       <c r="K3" t="n">
-        <v>44140803</v>
+        <v>10742524</v>
       </c>
       <c r="L3" t="n">
-        <v>50737825</v>
+        <v>12325049</v>
       </c>
       <c r="M3" t="n">
-        <v>61333613</v>
+        <v>15228047</v>
       </c>
       <c r="N3" t="n">
-        <v>65215290</v>
+        <v>16280676</v>
       </c>
       <c r="O3" t="n">
-        <v>63364172</v>
+        <v>15787184</v>
       </c>
       <c r="P3" t="n">
-        <v>64822976</v>
+        <v>16191529</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9385902881622314</v>
+        <v>0.8917977809906006</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8809911012649536</v>
+        <v>0.773406982421875</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7992766499519348</v>
+        <v>0.6379263997077942</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4997186064720154</v>
+        <v>0.2818076908588409</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8638978004455566</v>
+        <v>0.7315050363540649</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8957839608192444</v>
+        <v>0.7906033992767334</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,130 +926,130 @@
         <v>0.03188454573346271</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1184425</v>
+        <v>581172</v>
       </c>
       <c r="E4" t="n">
-        <v>11549304</v>
+        <v>2540283</v>
       </c>
       <c r="F4" t="n">
-        <v>348003</v>
+        <v>146985</v>
       </c>
       <c r="G4" t="n">
-        <v>8768</v>
+        <v>4763</v>
       </c>
       <c r="H4" t="n">
-        <v>17749</v>
+        <v>10529</v>
       </c>
       <c r="I4" t="n">
-        <v>1195</v>
+        <v>804</v>
       </c>
       <c r="J4" t="n">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>1257111</v>
+        <v>615216</v>
       </c>
       <c r="L4" t="n">
-        <v>1816730</v>
+        <v>806415</v>
       </c>
       <c r="M4" t="n">
-        <v>594937</v>
+        <v>253433</v>
       </c>
       <c r="N4" t="n">
-        <v>91549</v>
+        <v>45951</v>
       </c>
       <c r="O4" t="n">
-        <v>262682</v>
+        <v>119231</v>
       </c>
       <c r="P4" t="n">
-        <v>67832</v>
+        <v>31125</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999997079372406</v>
+        <v>0.9999955892562866</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9382991194725037</v>
+        <v>0.8858519792556763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8724528551101685</v>
+        <v>0.7661569714546204</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8161945343017578</v>
+        <v>0.6682947278022766</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5691417455673218</v>
+        <v>0.3138246536254883</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8669999837875366</v>
+        <v>0.7443519234657288</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9032293558120728</v>
+        <v>0.810217022895813</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>43066</v>
+        <v>20823</v>
       </c>
       <c r="E5" t="n">
-        <v>517942</v>
+        <v>234175</v>
       </c>
       <c r="F5" t="n">
-        <v>2985658</v>
+        <v>596155</v>
       </c>
       <c r="G5" t="n">
-        <v>37964</v>
+        <v>16629</v>
       </c>
       <c r="H5" t="n">
-        <v>143293</v>
+        <v>62140</v>
       </c>
       <c r="I5" t="n">
-        <v>7524</v>
+        <v>4595</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1244535</v>
+        <v>547315</v>
       </c>
       <c r="L5" t="n">
-        <v>1560141</v>
+        <v>744253</v>
       </c>
       <c r="M5" t="n">
-        <v>749792</v>
+        <v>338365</v>
       </c>
       <c r="N5" t="n">
-        <v>178681</v>
+        <v>64187</v>
       </c>
       <c r="O5" t="n">
-        <v>277260</v>
+        <v>136821</v>
       </c>
       <c r="P5" t="n">
-        <v>80579</v>
+        <v>40486</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999977350234985</v>
+        <v>0.9999966025352478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9619023203849792</v>
+        <v>0.9291830658912659</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9485734701156616</v>
+        <v>0.9055392146110535</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9795210361480713</v>
+        <v>0.9639499187469482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9958846569061279</v>
+        <v>0.9932908415794373</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9917771816253662</v>
+        <v>0.9844022989273071</v>
       </c>
       <c r="W5" t="n">
-        <v>0.997739851474762</v>
+        <v>0.9956377148628235</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>29480</v>
+        <v>13169</v>
       </c>
       <c r="E6" t="n">
-        <v>50652</v>
+        <v>18082</v>
       </c>
       <c r="F6" t="n">
-        <v>69029</v>
+        <v>22031</v>
       </c>
       <c r="G6" t="n">
-        <v>178480</v>
+        <v>25186</v>
       </c>
       <c r="H6" t="n">
-        <v>27323</v>
+        <v>9907</v>
       </c>
       <c r="I6" t="n">
-        <v>2161</v>
+        <v>982</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>19397</v>
+        <v>13368</v>
       </c>
       <c r="F7" t="n">
-        <v>159896</v>
+        <v>75866</v>
       </c>
       <c r="G7" t="n">
-        <v>40998</v>
+        <v>22835</v>
       </c>
       <c r="H7" t="n">
-        <v>1759886</v>
+        <v>372764</v>
       </c>
       <c r="I7" t="n">
-        <v>56881</v>
+        <v>24716</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>945</v>
+        <v>602</v>
       </c>
       <c r="F8" t="n">
-        <v>4136</v>
+        <v>2584</v>
       </c>
       <c r="G8" t="n">
-        <v>1660</v>
+        <v>939</v>
       </c>
       <c r="H8" t="n">
-        <v>73682</v>
+        <v>36310</v>
       </c>
       <c r="I8" t="n">
-        <v>692613</v>
+        <v>152860</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
